--- a/Config/Excel/color.xlsx
+++ b/Config/Excel/color.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11655"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1157,7 +1157,7 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B5" t="s">
         <v>9</v>
@@ -1168,7 +1168,7 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>11</v>
@@ -1179,7 +1179,7 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>13</v>
@@ -1190,7 +1190,7 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>15</v>
@@ -1201,7 +1201,7 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>17</v>
@@ -1212,7 +1212,7 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>19</v>
@@ -1223,7 +1223,7 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>21</v>
@@ -1234,7 +1234,7 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>23</v>
@@ -1245,7 +1245,7 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>25</v>
@@ -1256,7 +1256,7 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>27</v>
@@ -1267,7 +1267,7 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>29</v>
@@ -1278,7 +1278,7 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>31</v>
@@ -1289,42 +1289,42 @@
     </row>
     <row r="17" spans="1:1">
       <c r="A17">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
